--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU01/HRM/post DDV_HRM-2031-0252/Panel 7/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU01/HRM/post DDV_HRM-2031-0252/Panel 7/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Back_Summary.xlsx
@@ -413,28 +413,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="C1" t="inlineStr">
         <is>
-          <t>Distance 1</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Distance 2</t>
+          <t>Min Stepheight</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Angle</t>
+          <t>Mean Stepheight</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Area</t>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -444,22 +454,23 @@
           <t>Unit 7</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Fiducial 1</t>
-        </is>
-      </c>
       <c r="C2" t="n">
-        <v>119.57894</v>
+        <v>16.89783</v>
       </c>
       <c r="D2" t="n">
-        <v>85.60384999999999</v>
+        <v>16.43596</v>
       </c>
       <c r="E2" t="n">
-        <v>89.18566</v>
+        <v>16.69227</v>
       </c>
       <c r="F2" t="n">
-        <v>511.13306</v>
+        <v>42.46598</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.04927</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.8225</v>
       </c>
     </row>
     <row r="3">
@@ -469,16 +480,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>123.12368</v>
+        <v>16.86789</v>
       </c>
       <c r="D3" t="n">
-        <v>87.54689</v>
+        <v>16.39762</v>
       </c>
       <c r="E3" t="n">
-        <v>88.53366</v>
+        <v>16.40178</v>
       </c>
       <c r="F3" t="n">
-        <v>526.40191</v>
+        <v>42.70284</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.05075</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.83448</v>
       </c>
     </row>
     <row r="4">
@@ -488,16 +505,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>120.82437</v>
+        <v>16.74969</v>
       </c>
       <c r="D4" t="n">
-        <v>86.28055000000001</v>
+        <v>16.54223</v>
       </c>
       <c r="E4" t="n">
-        <v>89.54064</v>
+        <v>16.63838</v>
       </c>
       <c r="F4" t="n">
-        <v>509.74521</v>
+        <v>42.20907</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.05002</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.826</v>
       </c>
     </row>
     <row r="5">
@@ -507,16 +530,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>121.00442</v>
+        <v>16.70854</v>
       </c>
       <c r="D5" t="n">
-        <v>84.20809</v>
+        <v>16.30898</v>
       </c>
       <c r="E5" t="n">
-        <v>90.83983000000001</v>
+        <v>16.58077</v>
       </c>
       <c r="F5" t="n">
-        <v>521.83733</v>
+        <v>41.47152</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.04975</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.79667</v>
       </c>
     </row>
     <row r="6">
@@ -526,16 +555,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>122.26013</v>
+        <v>16.81377</v>
       </c>
       <c r="D6" t="n">
-        <v>83.45674</v>
+        <v>16.47914</v>
       </c>
       <c r="E6" t="n">
-        <v>89.04741</v>
+        <v>16.71551</v>
       </c>
       <c r="F6" t="n">
-        <v>508.85832</v>
+        <v>42.13066</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.05059</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.83669</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +580,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>122.77767</v>
+        <v>16.55961</v>
       </c>
       <c r="D7" t="n">
-        <v>85.75753</v>
+        <v>16.21062</v>
       </c>
       <c r="E7" t="n">
-        <v>89.79489</v>
+        <v>16.43547</v>
       </c>
       <c r="F7" t="n">
-        <v>515.25833</v>
+        <v>42.25197</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.05063</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.7951</v>
       </c>
     </row>
     <row r="8">
@@ -564,16 +605,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>120.90623</v>
+        <v>16.7422</v>
       </c>
       <c r="D8" t="n">
-        <v>85.6583</v>
+        <v>16.40608</v>
       </c>
       <c r="E8" t="n">
-        <v>90.69857</v>
+        <v>16.7272</v>
       </c>
       <c r="F8" t="n">
-        <v>515.29057</v>
+        <v>41.37255</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.05082</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.79397</v>
       </c>
     </row>
     <row r="9">
@@ -583,16 +630,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>121.46394</v>
+        <v>16.4257</v>
       </c>
       <c r="D9" t="n">
-        <v>84.67531</v>
+        <v>16.4165</v>
       </c>
       <c r="E9" t="n">
-        <v>90.00301</v>
+        <v>16.42138</v>
       </c>
       <c r="F9" t="n">
-        <v>523.61304</v>
+        <v>41.5836</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.05044</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.81385</v>
       </c>
     </row>
     <row r="10">
@@ -602,27 +655,53 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>121.6863</v>
+        <v>17.29653</v>
       </c>
       <c r="D10" t="n">
-        <v>84.77404</v>
+        <v>16.62807</v>
       </c>
       <c r="E10" t="n">
-        <v>90.67133</v>
+        <v>16.81073</v>
       </c>
       <c r="F10" t="n">
-        <v>515.40455</v>
+        <v>41.96323</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.04988</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.75596</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>Height</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Diameter</t>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -634,14 +713,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Micro Bump 3</t>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8.63325</v>
+        <v>16.86001</v>
       </c>
       <c r="D12" t="n">
-        <v>24.14886</v>
+        <v>16.05897</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16.47756</v>
+      </c>
+      <c r="F12" t="n">
+        <v>41.59092</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.05151</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.80975</v>
       </c>
     </row>
     <row r="13">
@@ -651,10 +742,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8.54815</v>
+        <v>16.55142</v>
       </c>
       <c r="D13" t="n">
-        <v>24.10972</v>
+        <v>16.3887</v>
+      </c>
+      <c r="E13" t="n">
+        <v>16.50663</v>
+      </c>
+      <c r="F13" t="n">
+        <v>42.37706</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.04996</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.82102</v>
       </c>
     </row>
     <row r="14">
@@ -664,10 +767,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8.63355</v>
+        <v>16.76106</v>
       </c>
       <c r="D14" t="n">
-        <v>23.76358</v>
+        <v>16.37366</v>
+      </c>
+      <c r="E14" t="n">
+        <v>16.51495</v>
+      </c>
+      <c r="F14" t="n">
+        <v>42.31462</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.04961</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.81905</v>
       </c>
     </row>
     <row r="15">
@@ -677,10 +792,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8.45697</v>
+        <v>16.85591</v>
       </c>
       <c r="D15" t="n">
-        <v>23.92467</v>
+        <v>16.51896</v>
+      </c>
+      <c r="E15" t="n">
+        <v>16.52629</v>
+      </c>
+      <c r="F15" t="n">
+        <v>42.20202</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.05091</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.82435</v>
       </c>
     </row>
     <row r="16">
@@ -690,10 +817,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8.521649999999999</v>
+        <v>16.65198</v>
       </c>
       <c r="D16" t="n">
-        <v>24.09531</v>
+        <v>16.4456</v>
+      </c>
+      <c r="E16" t="n">
+        <v>16.45961</v>
+      </c>
+      <c r="F16" t="n">
+        <v>41.99935</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.05054</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.79742</v>
       </c>
     </row>
     <row r="17">
@@ -703,10 +842,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8.545</v>
+        <v>16.52791</v>
       </c>
       <c r="D17" t="n">
-        <v>24.14532</v>
+        <v>16.26402</v>
+      </c>
+      <c r="E17" t="n">
+        <v>16.51541</v>
+      </c>
+      <c r="F17" t="n">
+        <v>42.40368</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.05054</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.80733</v>
       </c>
     </row>
     <row r="18">
@@ -716,10 +867,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8.40673</v>
+        <v>16.73638</v>
       </c>
       <c r="D18" t="n">
-        <v>24.74799</v>
+        <v>16.5647</v>
+      </c>
+      <c r="E18" t="n">
+        <v>16.69015</v>
+      </c>
+      <c r="F18" t="n">
+        <v>41.54715</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.05033</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.84139</v>
       </c>
     </row>
     <row r="19">
@@ -729,10 +892,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8.5526</v>
+        <v>16.96762</v>
       </c>
       <c r="D19" t="n">
-        <v>24.34609</v>
+        <v>16.74729</v>
+      </c>
+      <c r="E19" t="n">
+        <v>16.89919</v>
+      </c>
+      <c r="F19" t="n">
+        <v>42.83215</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.05033</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.77707</v>
       </c>
     </row>
     <row r="20">
@@ -742,272 +917,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8.49962</v>
+        <v>16.5749</v>
       </c>
       <c r="D20" t="n">
-        <v>24.36955</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Radius</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Pad 1</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>16.59408</v>
-      </c>
-      <c r="D22" t="n">
-        <v>16.69934</v>
-      </c>
-      <c r="E22" t="n">
-        <v>16.83708</v>
-      </c>
-      <c r="F22" t="n">
-        <v>42.29101</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.05151</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1.84632</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Unit 8</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>16.62686</v>
-      </c>
-      <c r="D23" t="n">
-        <v>16.53305</v>
-      </c>
-      <c r="E23" t="n">
-        <v>16.68355</v>
-      </c>
-      <c r="F23" t="n">
-        <v>42.52536</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.05063</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1.78224</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Unit 9</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>16.58892</v>
-      </c>
-      <c r="D24" t="n">
-        <v>16.38052</v>
-      </c>
-      <c r="E24" t="n">
-        <v>16.85971</v>
-      </c>
-      <c r="F24" t="n">
-        <v>43.26463</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.05082</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1.8355</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Unit 4</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>17.14624</v>
-      </c>
-      <c r="D25" t="n">
-        <v>16.63315</v>
-      </c>
-      <c r="E25" t="n">
-        <v>16.42838</v>
-      </c>
-      <c r="F25" t="n">
-        <v>42.48691</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.04965</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1.80644</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Unit 5</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>16.9637</v>
-      </c>
-      <c r="D26" t="n">
-        <v>16.34412</v>
-      </c>
-      <c r="E26" t="n">
-        <v>16.56496</v>
-      </c>
-      <c r="F26" t="n">
-        <v>42.03432</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.05039</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1.79902</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Unit 6</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>16.8725</v>
-      </c>
-      <c r="D27" t="n">
-        <v>16.38147</v>
-      </c>
-      <c r="E27" t="n">
-        <v>16.8111</v>
-      </c>
-      <c r="F27" t="n">
-        <v>43.08043</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.05018</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1.82213</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>16.78102</v>
-      </c>
-      <c r="D28" t="n">
-        <v>16.75167</v>
-      </c>
-      <c r="E28" t="n">
-        <v>16.79079</v>
-      </c>
-      <c r="F28" t="n">
-        <v>42.36043</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.05066</v>
-      </c>
-      <c r="H28" t="n">
-        <v>1.79969</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>16.42919</v>
-      </c>
-      <c r="D29" t="n">
-        <v>16.77552</v>
-      </c>
-      <c r="E29" t="n">
-        <v>16.95318</v>
-      </c>
-      <c r="F29" t="n">
-        <v>41.78198</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.04971</v>
-      </c>
-      <c r="H29" t="n">
-        <v>1.80649</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>16.38094</v>
-      </c>
-      <c r="D30" t="n">
-        <v>17.19714</v>
-      </c>
-      <c r="E30" t="n">
-        <v>16.96181</v>
-      </c>
-      <c r="F30" t="n">
-        <v>41.39316</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.05037</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1.79278</v>
+        <v>16.35564</v>
+      </c>
+      <c r="E20" t="n">
+        <v>16.4505</v>
+      </c>
+      <c r="F20" t="n">
+        <v>41.77062</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.05009</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.80561</v>
       </c>
     </row>
   </sheetData>
